--- a/outputs/Fuel_(petrol-gasoline,_parallel_market)_percentile_classification_matrix.xlsx
+++ b/outputs/Fuel_(petrol-gasoline,_parallel_market)_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2940" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2940" uniqueCount="149">
   <si>
     <t>2018 Mar</t>
   </si>
@@ -395,6 +395,9 @@
   </si>
   <si>
     <t>Yambio</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>Minimal</t>
@@ -1207,25 +1210,25 @@
         <v>127</v>
       </c>
       <c r="X2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Z2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AB2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AC2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AD2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AE2" t="s">
         <v>127</v>
@@ -1234,46 +1237,46 @@
         <v>127</v>
       </c>
       <c r="AG2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH2" t="s">
         <v>127</v>
       </c>
       <c r="AI2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AJ2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AK2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AL2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AN2" t="s">
         <v>127</v>
       </c>
       <c r="AO2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AP2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AR2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AS2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AT2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AU2" t="s">
         <v>127</v>
@@ -1423,13 +1426,13 @@
         <v>127</v>
       </c>
       <c r="CR2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CS2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CT2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:98">
@@ -1548,25 +1551,25 @@
         <v>127</v>
       </c>
       <c r="AM3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AN3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AP3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AR3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AS3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AT3" t="s">
         <v>127</v>
@@ -1584,58 +1587,58 @@
         <v>127</v>
       </c>
       <c r="AY3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AZ3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BA3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BB3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BC3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BD3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BE3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BF3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BG3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BH3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ3" t="s">
         <v>127</v>
       </c>
       <c r="BK3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BQ3" t="s">
         <v>127</v>
@@ -1653,10 +1656,10 @@
         <v>127</v>
       </c>
       <c r="BV3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BX3" t="s">
         <v>127</v>
@@ -1668,28 +1671,28 @@
         <v>127</v>
       </c>
       <c r="CA3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CB3" t="s">
         <v>127</v>
       </c>
       <c r="CC3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CD3" t="s">
         <v>127</v>
       </c>
       <c r="CE3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CF3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CG3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CH3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CI3" t="s">
         <v>127</v>
@@ -1698,16 +1701,16 @@
         <v>127</v>
       </c>
       <c r="CK3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CL3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CM3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CN3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CO3" t="s">
         <v>127</v>
@@ -1719,13 +1722,13 @@
         <v>127</v>
       </c>
       <c r="CR3" t="s">
+        <v>132</v>
+      </c>
+      <c r="CS3" t="s">
         <v>131</v>
       </c>
-      <c r="CS3" t="s">
-        <v>130</v>
-      </c>
       <c r="CT3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:98">
@@ -1733,22 +1736,22 @@
         <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D4" t="s">
         <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H4" t="s">
         <v>127</v>
@@ -1757,46 +1760,46 @@
         <v>127</v>
       </c>
       <c r="J4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O4" t="s">
         <v>127</v>
       </c>
       <c r="P4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="V4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="W4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="X4" t="s">
         <v>127</v>
@@ -1805,7 +1808,7 @@
         <v>127</v>
       </c>
       <c r="Z4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA4" t="s">
         <v>127</v>
@@ -1814,40 +1817,40 @@
         <v>127</v>
       </c>
       <c r="AC4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AD4" t="s">
         <v>127</v>
       </c>
       <c r="AE4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AF4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AI4" t="s">
         <v>127</v>
       </c>
       <c r="AJ4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AK4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AL4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM4" t="s">
         <v>127</v>
       </c>
       <c r="AN4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO4" t="s">
         <v>127</v>
@@ -1856,16 +1859,16 @@
         <v>127</v>
       </c>
       <c r="AQ4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AR4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AS4" t="s">
         <v>127</v>
       </c>
       <c r="AT4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AU4" t="s">
         <v>127</v>
@@ -1874,133 +1877,133 @@
         <v>127</v>
       </c>
       <c r="AW4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AX4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AY4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AZ4" t="s">
         <v>127</v>
       </c>
       <c r="BA4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BB4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BC4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BD4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BE4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BF4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BG4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BH4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP4" t="s">
         <v>127</v>
       </c>
       <c r="BQ4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BR4" t="s">
+        <v>130</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>127</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>127</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>127</v>
+      </c>
+      <c r="BW4" t="s">
         <v>129</v>
       </c>
-      <c r="BS4" t="s">
-        <v>127</v>
-      </c>
-      <c r="BT4" t="s">
-        <v>127</v>
-      </c>
-      <c r="BU4" t="s">
-        <v>127</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>127</v>
-      </c>
-      <c r="BW4" t="s">
-        <v>128</v>
-      </c>
       <c r="BX4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BY4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BZ4" t="s">
         <v>127</v>
       </c>
       <c r="CA4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CB4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CC4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CD4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CE4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CF4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CG4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CH4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CI4" t="s">
         <v>127</v>
       </c>
       <c r="CJ4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CK4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CL4" t="s">
         <v>127</v>
       </c>
       <c r="CM4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CN4" t="s">
         <v>127</v>
@@ -2015,13 +2018,13 @@
         <v>127</v>
       </c>
       <c r="CR4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="CS4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CT4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:98">
@@ -2146,52 +2149,52 @@
         <v>127</v>
       </c>
       <c r="AO5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AP5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AR5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AS5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AT5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AU5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AV5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AW5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AX5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AY5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AZ5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BA5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BB5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BC5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BD5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BE5" t="s">
         <v>127</v>
@@ -2200,106 +2203,106 @@
         <v>127</v>
       </c>
       <c r="BG5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BH5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BQ5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BR5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BS5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BT5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BU5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BV5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BX5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BY5" t="s">
+        <v>130</v>
+      </c>
+      <c r="BZ5" t="s">
+        <v>130</v>
+      </c>
+      <c r="CA5" t="s">
+        <v>130</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>130</v>
+      </c>
+      <c r="CC5" t="s">
+        <v>127</v>
+      </c>
+      <c r="CD5" t="s">
+        <v>127</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>130</v>
+      </c>
+      <c r="CF5" t="s">
+        <v>130</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH5" t="s">
+        <v>127</v>
+      </c>
+      <c r="CI5" t="s">
         <v>129</v>
       </c>
-      <c r="BZ5" t="s">
-        <v>129</v>
-      </c>
-      <c r="CA5" t="s">
-        <v>129</v>
-      </c>
-      <c r="CB5" t="s">
-        <v>129</v>
-      </c>
-      <c r="CC5" t="s">
-        <v>127</v>
-      </c>
-      <c r="CD5" t="s">
-        <v>127</v>
-      </c>
-      <c r="CE5" t="s">
-        <v>129</v>
-      </c>
-      <c r="CF5" t="s">
-        <v>129</v>
-      </c>
-      <c r="CG5" t="s">
-        <v>127</v>
-      </c>
-      <c r="CH5" t="s">
-        <v>127</v>
-      </c>
-      <c r="CI5" t="s">
-        <v>128</v>
-      </c>
       <c r="CJ5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CK5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CL5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CM5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CN5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CO5" t="s">
         <v>127</v>
@@ -2311,13 +2314,13 @@
         <v>127</v>
       </c>
       <c r="CR5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="CS5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="CT5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:98">
@@ -2442,133 +2445,133 @@
         <v>127</v>
       </c>
       <c r="AO6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AP6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AR6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AS6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AT6" t="s">
         <v>127</v>
       </c>
       <c r="AU6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AV6" t="s">
         <v>127</v>
       </c>
       <c r="AW6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AX6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AY6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AZ6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BA6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BB6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BC6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BD6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BE6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BF6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BG6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BH6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BQ6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BR6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BS6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BT6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BU6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BV6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BX6" t="s">
         <v>127</v>
       </c>
       <c r="BY6" t="s">
+        <v>130</v>
+      </c>
+      <c r="BZ6" t="s">
+        <v>130</v>
+      </c>
+      <c r="CA6" t="s">
+        <v>127</v>
+      </c>
+      <c r="CB6" t="s">
         <v>129</v>
       </c>
-      <c r="BZ6" t="s">
-        <v>129</v>
-      </c>
-      <c r="CA6" t="s">
-        <v>127</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>128</v>
-      </c>
       <c r="CC6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CD6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CE6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CF6" t="s">
         <v>127</v>
@@ -2607,13 +2610,13 @@
         <v>127</v>
       </c>
       <c r="CR6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="CS6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="CT6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:98">
@@ -2798,13 +2801,13 @@
         <v>127</v>
       </c>
       <c r="BI7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL7" t="s">
         <v>127</v>
@@ -2846,10 +2849,10 @@
         <v>127</v>
       </c>
       <c r="BY7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BZ7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CA7" t="s">
         <v>127</v>
@@ -2885,10 +2888,10 @@
         <v>127</v>
       </c>
       <c r="CL7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CM7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CN7" t="s">
         <v>127</v>
@@ -2903,13 +2906,13 @@
         <v>127</v>
       </c>
       <c r="CR7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CS7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CT7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:98">
@@ -3037,79 +3040,79 @@
         <v>127</v>
       </c>
       <c r="AP8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AR8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AS8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AT8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AU8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AV8" t="s">
         <v>127</v>
       </c>
       <c r="AW8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AX8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AY8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AZ8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BA8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BB8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BC8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BD8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BE8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BF8" t="s">
         <v>127</v>
       </c>
       <c r="BG8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BH8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO8" t="s">
         <v>127</v>
@@ -3130,28 +3133,28 @@
         <v>127</v>
       </c>
       <c r="BU8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BV8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW8" t="s">
         <v>127</v>
       </c>
       <c r="BX8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BY8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BZ8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CA8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CB8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CC8" t="s">
         <v>127</v>
@@ -3163,7 +3166,7 @@
         <v>127</v>
       </c>
       <c r="CF8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CG8" t="s">
         <v>127</v>
@@ -3199,13 +3202,13 @@
         <v>127</v>
       </c>
       <c r="CR8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="CS8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CT8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:98">
@@ -3213,19 +3216,19 @@
         <v>105</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C9" t="s">
         <v>127</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G9" t="s">
         <v>127</v>
@@ -3237,115 +3240,115 @@
         <v>127</v>
       </c>
       <c r="J9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L9" t="s">
         <v>127</v>
       </c>
       <c r="M9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U9" t="s">
         <v>127</v>
       </c>
       <c r="V9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="W9" t="s">
         <v>127</v>
       </c>
       <c r="X9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Z9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AB9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AC9" t="s">
         <v>127</v>
       </c>
       <c r="AD9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AE9" t="s">
         <v>127</v>
       </c>
       <c r="AF9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG9" t="s">
         <v>127</v>
       </c>
       <c r="AH9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AI9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AJ9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AK9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AL9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AN9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AP9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AR9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AS9" t="s">
         <v>127</v>
       </c>
       <c r="AT9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AU9" t="s">
         <v>127</v>
@@ -3354,7 +3357,7 @@
         <v>127</v>
       </c>
       <c r="AW9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AX9" t="s">
         <v>127</v>
@@ -3363,19 +3366,19 @@
         <v>127</v>
       </c>
       <c r="AZ9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BA9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BB9" t="s">
         <v>127</v>
       </c>
       <c r="BC9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BD9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BE9" t="s">
         <v>127</v>
@@ -3387,28 +3390,28 @@
         <v>127</v>
       </c>
       <c r="BH9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN9" t="s">
         <v>127</v>
       </c>
       <c r="BO9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP9" t="s">
         <v>127</v>
@@ -3495,13 +3498,13 @@
         <v>127</v>
       </c>
       <c r="CR9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CS9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CT9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:98">
@@ -3698,7 +3701,7 @@
         <v>127</v>
       </c>
       <c r="BM10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN10" t="s">
         <v>127</v>
@@ -3788,16 +3791,16 @@
         <v>127</v>
       </c>
       <c r="CQ10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CR10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CS10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CT10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:98">
@@ -4057,19 +4060,19 @@
         <v>127</v>
       </c>
       <c r="CH11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CI11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CJ11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CK11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CL11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CM11" t="s">
         <v>127</v>
@@ -4087,13 +4090,13 @@
         <v>127</v>
       </c>
       <c r="CR11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CS11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CT11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:98">
@@ -4362,13 +4365,13 @@
         <v>127</v>
       </c>
       <c r="CK12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CL12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CM12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CN12" t="s">
         <v>127</v>
@@ -4383,13 +4386,13 @@
         <v>127</v>
       </c>
       <c r="CR12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CS12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CT12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:98">
@@ -4574,103 +4577,103 @@
         <v>127</v>
       </c>
       <c r="BI13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ13" t="s">
         <v>127</v>
       </c>
       <c r="BK13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BQ13" t="s">
         <v>127</v>
       </c>
       <c r="BR13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BS13" t="s">
         <v>127</v>
       </c>
       <c r="BT13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BU13" t="s">
         <v>127</v>
       </c>
       <c r="BV13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BX13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BY13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BZ13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CA13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CB13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CC13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD13" t="s">
         <v>127</v>
       </c>
       <c r="CE13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CF13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CG13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CH13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CI13" t="s">
+        <v>130</v>
+      </c>
+      <c r="CJ13" t="s">
         <v>129</v>
       </c>
-      <c r="CJ13" t="s">
-        <v>128</v>
-      </c>
       <c r="CK13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CL13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CM13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CN13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CO13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CP13" t="s">
         <v>127</v>
@@ -4679,13 +4682,13 @@
         <v>127</v>
       </c>
       <c r="CR13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CS13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CT13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:98">
@@ -4867,43 +4870,43 @@
         <v>127</v>
       </c>
       <c r="BH14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BQ14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BR14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BS14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BT14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BU14" t="s">
         <v>127</v>
@@ -4942,16 +4945,16 @@
         <v>127</v>
       </c>
       <c r="CG14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CH14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CI14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CJ14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CK14" t="s">
         <v>127</v>
@@ -4960,28 +4963,28 @@
         <v>127</v>
       </c>
       <c r="CM14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CN14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CO14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CP14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CQ14" t="s">
         <v>127</v>
       </c>
       <c r="CR14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CS14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CT14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:98">
@@ -5019,28 +5022,28 @@
         <v>127</v>
       </c>
       <c r="L15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T15" t="s">
         <v>127</v>
@@ -5049,10 +5052,10 @@
         <v>127</v>
       </c>
       <c r="V15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="W15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="X15" t="s">
         <v>127</v>
@@ -5064,58 +5067,58 @@
         <v>127</v>
       </c>
       <c r="AA15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AB15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AC15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AD15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AE15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AF15" t="s">
         <v>127</v>
       </c>
       <c r="AG15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH15" t="s">
         <v>127</v>
       </c>
       <c r="AI15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AJ15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AK15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AL15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AN15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AP15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AR15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AS15" t="s">
         <v>127</v>
@@ -5124,34 +5127,34 @@
         <v>127</v>
       </c>
       <c r="AU15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AV15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AW15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AX15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AY15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AZ15" t="s">
         <v>127</v>
       </c>
       <c r="BA15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BB15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BC15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BD15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BE15" t="s">
         <v>127</v>
@@ -5160,34 +5163,34 @@
         <v>127</v>
       </c>
       <c r="BG15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BH15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM15" t="s">
         <v>127</v>
       </c>
       <c r="BN15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO15" t="s">
         <v>127</v>
       </c>
       <c r="BP15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BQ15" t="s">
         <v>127</v>
@@ -5199,64 +5202,64 @@
         <v>127</v>
       </c>
       <c r="BT15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BU15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BV15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BX15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BY15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BZ15" t="s">
         <v>127</v>
       </c>
       <c r="CA15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CB15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CC15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD15" t="s">
         <v>127</v>
       </c>
       <c r="CE15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CF15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CG15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CH15" t="s">
         <v>127</v>
       </c>
       <c r="CI15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CJ15" t="s">
         <v>127</v>
       </c>
       <c r="CK15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CL15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CM15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CN15" t="s">
         <v>127</v>
@@ -5271,13 +5274,13 @@
         <v>127</v>
       </c>
       <c r="CR15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="CS15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CT15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:98">
@@ -5285,10 +5288,10 @@
         <v>112</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D16" t="s">
         <v>127</v>
@@ -5297,7 +5300,7 @@
         <v>127</v>
       </c>
       <c r="F16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G16" t="s">
         <v>127</v>
@@ -5459,28 +5462,28 @@
         <v>127</v>
       </c>
       <c r="BH16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ16" t="s">
         <v>127</v>
       </c>
       <c r="BK16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP16" t="s">
         <v>127</v>
@@ -5489,76 +5492,76 @@
         <v>127</v>
       </c>
       <c r="BR16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BS16" t="s">
         <v>127</v>
       </c>
       <c r="BT16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BU16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BV16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BX16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BY16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BZ16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CA16" t="s">
         <v>127</v>
       </c>
       <c r="CB16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CC16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CE16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CF16" t="s">
+        <v>130</v>
+      </c>
+      <c r="CG16" t="s">
         <v>129</v>
       </c>
-      <c r="CG16" t="s">
-        <v>128</v>
-      </c>
       <c r="CH16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CI16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CJ16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CK16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="CL16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CM16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CN16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CO16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CP16" t="s">
         <v>127</v>
@@ -5567,13 +5570,13 @@
         <v>127</v>
       </c>
       <c r="CR16" t="s">
+        <v>137</v>
+      </c>
+      <c r="CS16" t="s">
+        <v>142</v>
+      </c>
+      <c r="CT16" t="s">
         <v>136</v>
-      </c>
-      <c r="CS16" t="s">
-        <v>141</v>
-      </c>
-      <c r="CT16" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:98">
@@ -5665,19 +5668,19 @@
         <v>127</v>
       </c>
       <c r="AD17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AE17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AF17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AI17" t="s">
         <v>127</v>
@@ -5752,10 +5755,10 @@
         <v>127</v>
       </c>
       <c r="BG17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BH17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI17" t="s">
         <v>127</v>
@@ -5764,28 +5767,28 @@
         <v>127</v>
       </c>
       <c r="BK17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL17" t="s">
         <v>127</v>
       </c>
       <c r="BM17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BQ17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BR17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BS17" t="s">
         <v>127</v>
@@ -5797,13 +5800,13 @@
         <v>127</v>
       </c>
       <c r="BV17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BX17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BY17" t="s">
         <v>127</v>
@@ -5818,10 +5821,10 @@
         <v>127</v>
       </c>
       <c r="CC17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="CD17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CE17" t="s">
         <v>127</v>
@@ -5833,7 +5836,7 @@
         <v>127</v>
       </c>
       <c r="CH17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CI17" t="s">
         <v>127</v>
@@ -5863,13 +5866,13 @@
         <v>127</v>
       </c>
       <c r="CR17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CS17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CT17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:98">
@@ -5943,118 +5946,118 @@
         <v>127</v>
       </c>
       <c r="X18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Z18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA18" t="s">
         <v>127</v>
       </c>
       <c r="AB18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AC18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AD18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AE18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AF18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AI18" t="s">
         <v>127</v>
       </c>
       <c r="AJ18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AK18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AL18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AN18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AP18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AR18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AS18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AT18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AU18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AV18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AW18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AX18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AY18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AZ18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BA18" t="s">
         <v>127</v>
       </c>
       <c r="BB18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BC18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BD18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BE18" t="s">
         <v>127</v>
       </c>
       <c r="BF18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BG18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BH18" t="s">
         <v>127</v>
       </c>
       <c r="BI18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ18" t="s">
         <v>127</v>
@@ -6063,25 +6066,25 @@
         <v>127</v>
       </c>
       <c r="BL18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP18" t="s">
         <v>127</v>
       </c>
       <c r="BQ18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BR18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BS18" t="s">
         <v>127</v>
@@ -6093,46 +6096,46 @@
         <v>127</v>
       </c>
       <c r="BV18" t="s">
+        <v>130</v>
+      </c>
+      <c r="BW18" t="s">
+        <v>128</v>
+      </c>
+      <c r="BX18" t="s">
+        <v>130</v>
+      </c>
+      <c r="BY18" t="s">
+        <v>130</v>
+      </c>
+      <c r="BZ18" t="s">
+        <v>130</v>
+      </c>
+      <c r="CA18" t="s">
+        <v>130</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>130</v>
+      </c>
+      <c r="CC18" t="s">
         <v>129</v>
       </c>
-      <c r="BW18" t="s">
-        <v>127</v>
-      </c>
-      <c r="BX18" t="s">
-        <v>129</v>
-      </c>
-      <c r="BY18" t="s">
-        <v>129</v>
-      </c>
-      <c r="BZ18" t="s">
-        <v>129</v>
-      </c>
-      <c r="CA18" t="s">
-        <v>129</v>
-      </c>
-      <c r="CB18" t="s">
-        <v>129</v>
-      </c>
-      <c r="CC18" t="s">
-        <v>128</v>
-      </c>
       <c r="CD18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CE18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CF18" t="s">
         <v>127</v>
       </c>
       <c r="CG18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CH18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CI18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CJ18" t="s">
         <v>127</v>
@@ -6141,16 +6144,16 @@
         <v>127</v>
       </c>
       <c r="CL18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CM18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CN18" t="s">
         <v>127</v>
       </c>
       <c r="CO18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CP18" t="s">
         <v>127</v>
@@ -6159,13 +6162,13 @@
         <v>127</v>
       </c>
       <c r="CR18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="CS18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CT18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:98">
@@ -6173,7 +6176,7 @@
         <v>115</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C19" t="s">
         <v>127</v>
@@ -6194,7 +6197,7 @@
         <v>127</v>
       </c>
       <c r="I19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J19" t="s">
         <v>127</v>
@@ -6203,28 +6206,28 @@
         <v>127</v>
       </c>
       <c r="L19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T19" t="s">
         <v>127</v>
@@ -6233,7 +6236,7 @@
         <v>127</v>
       </c>
       <c r="V19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="W19" t="s">
         <v>127</v>
@@ -6242,7 +6245,7 @@
         <v>127</v>
       </c>
       <c r="Y19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Z19" t="s">
         <v>127</v>
@@ -6251,142 +6254,142 @@
         <v>127</v>
       </c>
       <c r="AB19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AC19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AD19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AE19" t="s">
         <v>127</v>
       </c>
       <c r="AF19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AI19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AJ19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AK19" t="s">
         <v>127</v>
       </c>
       <c r="AL19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AN19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO19" t="s">
         <v>127</v>
       </c>
       <c r="AP19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ19" t="s">
         <v>127</v>
       </c>
       <c r="AR19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AS19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AT19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AU19" t="s">
         <v>127</v>
       </c>
       <c r="AV19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AW19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AX19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AY19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AZ19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BA19" t="s">
         <v>127</v>
       </c>
       <c r="BB19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BC19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BD19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BE19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BF19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BG19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BH19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BK19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BQ19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BR19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BS19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BT19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BU19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BV19" t="s">
         <v>127</v>
@@ -6398,70 +6401,70 @@
         <v>127</v>
       </c>
       <c r="BY19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BZ19" t="s">
         <v>127</v>
       </c>
       <c r="CA19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="CB19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="CC19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CD19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CE19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CF19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CG19" t="s">
         <v>127</v>
       </c>
       <c r="CH19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CI19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CJ19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CK19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CL19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CM19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CN19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CO19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CP19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CQ19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CR19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="CS19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="CT19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:98">
@@ -6550,10 +6553,10 @@
         <v>127</v>
       </c>
       <c r="AC20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AD20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AE20" t="s">
         <v>127</v>
@@ -6577,43 +6580,43 @@
         <v>127</v>
       </c>
       <c r="AL20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AN20" t="s">
         <v>127</v>
       </c>
       <c r="AO20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AP20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ20" t="s">
         <v>127</v>
       </c>
       <c r="AR20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AS20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AT20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AU20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AV20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AW20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AX20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AY20" t="s">
         <v>127</v>
@@ -6625,28 +6628,28 @@
         <v>127</v>
       </c>
       <c r="BB20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BC20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BD20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BE20" t="s">
         <v>127</v>
       </c>
       <c r="BF20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BG20" t="s">
         <v>127</v>
       </c>
       <c r="BH20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ20" t="s">
         <v>127</v>
@@ -6655,10 +6658,10 @@
         <v>127</v>
       </c>
       <c r="BL20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN20" t="s">
         <v>127</v>
@@ -6694,7 +6697,7 @@
         <v>127</v>
       </c>
       <c r="BY20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BZ20" t="s">
         <v>127</v>
@@ -6751,13 +6754,13 @@
         <v>127</v>
       </c>
       <c r="CR20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CS20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CT20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:98">
@@ -6765,40 +6768,40 @@
         <v>117</v>
       </c>
       <c r="B21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F21" t="s">
         <v>127</v>
       </c>
       <c r="G21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K21" t="s">
         <v>127</v>
       </c>
       <c r="L21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N21" t="s">
         <v>127</v>
@@ -6807,142 +6810,142 @@
         <v>127</v>
       </c>
       <c r="P21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="V21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="W21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="X21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Z21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AB21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AC21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AD21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AE21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AF21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AI21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AJ21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AK21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AL21" t="s">
         <v>127</v>
       </c>
       <c r="AM21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AN21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AP21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AR21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AS21" t="s">
         <v>127</v>
       </c>
       <c r="AT21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AU21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AV21" t="s">
         <v>127</v>
       </c>
       <c r="AW21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AX21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AY21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AZ21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BA21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BB21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BC21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BD21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BE21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BF21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BG21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BH21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ21" t="s">
         <v>127</v>
@@ -6951,109 +6954,109 @@
         <v>127</v>
       </c>
       <c r="BL21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BQ21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BR21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BS21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BT21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BU21" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BV21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW21" t="s">
         <v>127</v>
       </c>
       <c r="BX21" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BY21" t="s">
         <v>127</v>
       </c>
       <c r="BZ21" t="s">
+        <v>130</v>
+      </c>
+      <c r="CA21" t="s">
+        <v>130</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>130</v>
+      </c>
+      <c r="CC21" t="s">
+        <v>130</v>
+      </c>
+      <c r="CD21" t="s">
+        <v>130</v>
+      </c>
+      <c r="CE21" t="s">
+        <v>130</v>
+      </c>
+      <c r="CF21" t="s">
+        <v>130</v>
+      </c>
+      <c r="CG21" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH21" t="s">
         <v>129</v>
       </c>
-      <c r="CA21" t="s">
-        <v>129</v>
-      </c>
-      <c r="CB21" t="s">
-        <v>129</v>
-      </c>
-      <c r="CC21" t="s">
-        <v>129</v>
-      </c>
-      <c r="CD21" t="s">
-        <v>129</v>
-      </c>
-      <c r="CE21" t="s">
-        <v>129</v>
-      </c>
-      <c r="CF21" t="s">
-        <v>129</v>
-      </c>
-      <c r="CG21" t="s">
-        <v>127</v>
-      </c>
-      <c r="CH21" t="s">
-        <v>128</v>
-      </c>
       <c r="CI21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CJ21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CK21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CL21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CM21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CN21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CO21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CP21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CQ21" t="s">
         <v>127</v>
       </c>
       <c r="CR21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="CS21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="CT21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:98">
@@ -7247,10 +7250,10 @@
         <v>127</v>
       </c>
       <c r="BL22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN22" t="s">
         <v>127</v>
@@ -7265,28 +7268,28 @@
         <v>127</v>
       </c>
       <c r="BR22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BS22" t="s">
         <v>127</v>
       </c>
       <c r="BT22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BU22" t="s">
         <v>127</v>
       </c>
       <c r="BV22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BX22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BY22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BZ22" t="s">
         <v>127</v>
@@ -7304,10 +7307,10 @@
         <v>127</v>
       </c>
       <c r="CE22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CF22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CG22" t="s">
         <v>127</v>
@@ -7343,13 +7346,13 @@
         <v>127</v>
       </c>
       <c r="CR22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CS22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CT22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:98">
@@ -7423,7 +7426,7 @@
         <v>127</v>
       </c>
       <c r="X23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y23" t="s">
         <v>127</v>
@@ -7432,16 +7435,16 @@
         <v>127</v>
       </c>
       <c r="AA23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AB23" t="s">
         <v>127</v>
       </c>
       <c r="AC23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AD23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AE23" t="s">
         <v>127</v>
@@ -7459,7 +7462,7 @@
         <v>127</v>
       </c>
       <c r="AJ23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AK23" t="s">
         <v>127</v>
@@ -7498,7 +7501,7 @@
         <v>127</v>
       </c>
       <c r="AW23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AX23" t="s">
         <v>127</v>
@@ -7510,7 +7513,7 @@
         <v>127</v>
       </c>
       <c r="BA23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BB23" t="s">
         <v>127</v>
@@ -7519,82 +7522,82 @@
         <v>127</v>
       </c>
       <c r="BD23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BE23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BF23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BG23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BH23" t="s">
         <v>127</v>
       </c>
       <c r="BI23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL23" t="s">
         <v>127</v>
       </c>
       <c r="BM23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BQ23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BR23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BS23" t="s">
         <v>127</v>
       </c>
       <c r="BT23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BU23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BV23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BX23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BY23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BZ23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CA23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CB23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CC23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD23" t="s">
         <v>127</v>
@@ -7603,7 +7606,7 @@
         <v>127</v>
       </c>
       <c r="CF23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CG23" t="s">
         <v>127</v>
@@ -7618,19 +7621,19 @@
         <v>127</v>
       </c>
       <c r="CK23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CL23" t="s">
         <v>127</v>
       </c>
       <c r="CM23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CN23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CO23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CP23" t="s">
         <v>127</v>
@@ -7639,13 +7642,13 @@
         <v>127</v>
       </c>
       <c r="CR23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="CS23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CT23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:98">
@@ -7656,7 +7659,7 @@
         <v>127</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
         <v>127</v>
@@ -7674,7 +7677,7 @@
         <v>127</v>
       </c>
       <c r="I24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J24" t="s">
         <v>127</v>
@@ -7683,19 +7686,19 @@
         <v>127</v>
       </c>
       <c r="L24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O24" t="s">
         <v>127</v>
       </c>
       <c r="P24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q24" t="s">
         <v>127</v>
@@ -7716,232 +7719,232 @@
         <v>127</v>
       </c>
       <c r="W24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="X24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y24" t="s">
         <v>127</v>
       </c>
       <c r="Z24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AB24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AC24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AD24" t="s">
         <v>127</v>
       </c>
       <c r="AE24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AF24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG24" t="s">
         <v>127</v>
       </c>
       <c r="AH24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AI24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AJ24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AK24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AL24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AN24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AP24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AR24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AS24" t="s">
         <v>127</v>
       </c>
       <c r="AT24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AU24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AV24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AW24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AX24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AY24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AZ24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BA24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BB24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BC24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BD24" t="s">
         <v>127</v>
       </c>
       <c r="BE24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BF24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BG24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BH24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK24" t="s">
         <v>127</v>
       </c>
       <c r="BL24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM24" t="s">
         <v>127</v>
       </c>
       <c r="BN24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BQ24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BR24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BS24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BT24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BU24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BV24" t="s">
+        <v>130</v>
+      </c>
+      <c r="BW24" t="s">
+        <v>130</v>
+      </c>
+      <c r="BX24" t="s">
         <v>129</v>
       </c>
-      <c r="BW24" t="s">
+      <c r="BY24" t="s">
+        <v>127</v>
+      </c>
+      <c r="BZ24" t="s">
+        <v>130</v>
+      </c>
+      <c r="CA24" t="s">
+        <v>130</v>
+      </c>
+      <c r="CB24" t="s">
         <v>129</v>
       </c>
-      <c r="BX24" t="s">
-        <v>128</v>
-      </c>
-      <c r="BY24" t="s">
-        <v>127</v>
-      </c>
-      <c r="BZ24" t="s">
+      <c r="CC24" t="s">
         <v>129</v>
       </c>
-      <c r="CA24" t="s">
-        <v>129</v>
-      </c>
-      <c r="CB24" t="s">
-        <v>128</v>
-      </c>
-      <c r="CC24" t="s">
-        <v>128</v>
-      </c>
       <c r="CD24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CE24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CF24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CG24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CH24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CI24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CJ24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CK24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CL24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CM24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CN24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CO24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CP24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CQ24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CR24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="CS24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="CT24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:98">
@@ -7961,22 +7964,22 @@
         <v>127</v>
       </c>
       <c r="F25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L25" t="s">
         <v>127</v>
@@ -8003,10 +8006,10 @@
         <v>127</v>
       </c>
       <c r="T25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="V25" t="s">
         <v>127</v>
@@ -8030,25 +8033,25 @@
         <v>127</v>
       </c>
       <c r="AC25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AD25" t="s">
         <v>127</v>
       </c>
       <c r="AE25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AF25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG25" t="s">
         <v>127</v>
       </c>
       <c r="AH25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AI25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AJ25" t="s">
         <v>127</v>
@@ -8057,187 +8060,187 @@
         <v>127</v>
       </c>
       <c r="AL25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AN25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AP25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ25" t="s">
         <v>127</v>
       </c>
       <c r="AR25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AS25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AT25" t="s">
         <v>127</v>
       </c>
       <c r="AU25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AV25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AW25" t="s">
         <v>127</v>
       </c>
       <c r="AX25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AY25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AZ25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BA25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BB25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BC25" t="s">
         <v>127</v>
       </c>
       <c r="BD25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BE25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BF25" t="s">
         <v>127</v>
       </c>
       <c r="BG25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BH25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL25" t="s">
         <v>127</v>
       </c>
       <c r="BM25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BQ25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BR25" t="s">
         <v>127</v>
       </c>
       <c r="BS25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BT25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BU25" t="s">
         <v>127</v>
       </c>
       <c r="BV25" t="s">
+        <v>130</v>
+      </c>
+      <c r="BW25" t="s">
         <v>129</v>
       </c>
-      <c r="BW25" t="s">
-        <v>128</v>
-      </c>
       <c r="BX25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BY25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BZ25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CA25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CB25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CC25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CD25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CE25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CF25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CG25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CH25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CI25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CJ25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CK25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CL25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CM25" t="s">
         <v>127</v>
       </c>
       <c r="CN25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CO25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CP25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CQ25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CR25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="CS25" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CT25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:98">
@@ -8458,58 +8461,58 @@
         <v>127</v>
       </c>
       <c r="BU26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BV26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BX26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BY26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BZ26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CA26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CB26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CC26" t="s">
         <v>127</v>
       </c>
       <c r="CD26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CE26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CF26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CG26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CH26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CI26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CJ26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CK26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CL26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CM26" t="s">
         <v>127</v>
@@ -8527,13 +8530,13 @@
         <v>127</v>
       </c>
       <c r="CR26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CS26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CT26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:98">
@@ -8544,10 +8547,10 @@
         <v>127</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E27" t="s">
         <v>127</v>
@@ -8712,13 +8715,13 @@
         <v>127</v>
       </c>
       <c r="BG27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BH27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ27" t="s">
         <v>127</v>
@@ -8727,25 +8730,25 @@
         <v>127</v>
       </c>
       <c r="BL27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM27" t="s">
         <v>127</v>
       </c>
       <c r="BN27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP27" t="s">
         <v>127</v>
       </c>
       <c r="BQ27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BR27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BS27" t="s">
         <v>127</v>
@@ -8823,13 +8826,13 @@
         <v>127</v>
       </c>
       <c r="CR27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CS27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CT27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:98">
@@ -8837,7 +8840,7 @@
         <v>124</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s">
         <v>127</v>
@@ -8984,22 +8987,22 @@
         <v>127</v>
       </c>
       <c r="AY28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AZ28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BA28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BB28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BC28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BD28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BE28" t="s">
         <v>127</v>
@@ -9008,34 +9011,34 @@
         <v>127</v>
       </c>
       <c r="BG28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BH28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI28" t="s">
         <v>127</v>
       </c>
       <c r="BJ28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK28" t="s">
         <v>127</v>
       </c>
       <c r="BL28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BQ28" t="s">
         <v>127</v>
@@ -9050,67 +9053,67 @@
         <v>127</v>
       </c>
       <c r="BU28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BV28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BX28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BY28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BZ28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CA28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CB28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CC28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CE28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CF28" t="s">
+        <v>130</v>
+      </c>
+      <c r="CG28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CJ28" t="s">
         <v>129</v>
       </c>
-      <c r="CG28" t="s">
-        <v>127</v>
-      </c>
-      <c r="CH28" t="s">
-        <v>127</v>
-      </c>
-      <c r="CI28" t="s">
-        <v>127</v>
-      </c>
-      <c r="CJ28" t="s">
-        <v>128</v>
-      </c>
       <c r="CK28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CL28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CM28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CN28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CO28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CP28" t="s">
         <v>127</v>
@@ -9119,13 +9122,13 @@
         <v>127</v>
       </c>
       <c r="CR28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CS28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CT28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:98">
@@ -9136,16 +9139,16 @@
         <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G29" t="s">
         <v>127</v>
@@ -9187,10 +9190,10 @@
         <v>127</v>
       </c>
       <c r="T29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="V29" t="s">
         <v>127</v>
@@ -9199,208 +9202,208 @@
         <v>127</v>
       </c>
       <c r="X29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Z29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AB29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AC29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AD29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AE29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AF29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AI29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AJ29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AK29" t="s">
         <v>127</v>
       </c>
       <c r="AL29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AN29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AP29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AR29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AS29" t="s">
         <v>127</v>
       </c>
       <c r="AT29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AU29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AV29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AW29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AX29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AY29" t="s">
         <v>127</v>
       </c>
       <c r="AZ29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BA29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BB29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BC29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BD29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BE29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BF29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BG29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BH29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK29" t="s">
         <v>127</v>
       </c>
       <c r="BL29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BQ29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BR29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BS29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BT29" t="s">
         <v>127</v>
       </c>
       <c r="BU29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BV29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW29" t="s">
+        <v>130</v>
+      </c>
+      <c r="BX29" t="s">
         <v>129</v>
       </c>
-      <c r="BX29" t="s">
-        <v>128</v>
-      </c>
       <c r="BY29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BZ29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="CA29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="CB29" t="s">
         <v>127</v>
       </c>
       <c r="CC29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CD29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CE29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CF29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CG29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CH29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CI29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CJ29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CK29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CL29" t="s">
         <v>127</v>
       </c>
       <c r="CM29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="CN29" t="s">
         <v>127</v>
@@ -9415,13 +9418,13 @@
         <v>127</v>
       </c>
       <c r="CR29" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="CS29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="CT29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:98">
@@ -9432,7 +9435,7 @@
         <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s">
         <v>127</v>
@@ -9450,13 +9453,13 @@
         <v>127</v>
       </c>
       <c r="I30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J30" t="s">
         <v>127</v>
       </c>
       <c r="K30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L30" t="s">
         <v>127</v>
@@ -9465,73 +9468,73 @@
         <v>127</v>
       </c>
       <c r="N30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P30" t="s">
         <v>127</v>
       </c>
       <c r="Q30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R30" t="s">
         <v>127</v>
       </c>
       <c r="S30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U30" t="s">
         <v>127</v>
       </c>
       <c r="V30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="W30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="X30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Z30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AB30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AC30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AD30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AE30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AF30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG30" t="s">
         <v>127</v>
       </c>
       <c r="AH30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AI30" t="s">
         <v>127</v>
       </c>
       <c r="AJ30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AK30" t="s">
         <v>127</v>
@@ -9552,7 +9555,7 @@
         <v>127</v>
       </c>
       <c r="AQ30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AR30" t="s">
         <v>127</v>
@@ -9582,7 +9585,7 @@
         <v>127</v>
       </c>
       <c r="BA30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BB30" t="s">
         <v>127</v>
@@ -9603,121 +9606,121 @@
         <v>127</v>
       </c>
       <c r="BH30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BJ30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BO30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BP30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BQ30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BR30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BS30" t="s">
         <v>127</v>
       </c>
       <c r="BT30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BU30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BV30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BX30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BY30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BZ30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CA30" t="s">
+        <v>130</v>
+      </c>
+      <c r="CB30" t="s">
         <v>129</v>
       </c>
-      <c r="CB30" t="s">
-        <v>128</v>
-      </c>
       <c r="CC30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CD30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CE30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CF30" t="s">
+        <v>130</v>
+      </c>
+      <c r="CG30" t="s">
+        <v>130</v>
+      </c>
+      <c r="CH30" t="s">
+        <v>130</v>
+      </c>
+      <c r="CI30" t="s">
+        <v>130</v>
+      </c>
+      <c r="CJ30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CK30" t="s">
         <v>129</v>
       </c>
-      <c r="CG30" t="s">
+      <c r="CL30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM30" t="s">
+        <v>130</v>
+      </c>
+      <c r="CN30" t="s">
         <v>129</v>
       </c>
-      <c r="CH30" t="s">
-        <v>129</v>
-      </c>
-      <c r="CI30" t="s">
-        <v>129</v>
-      </c>
-      <c r="CJ30" t="s">
-        <v>127</v>
-      </c>
-      <c r="CK30" t="s">
-        <v>128</v>
-      </c>
-      <c r="CL30" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM30" t="s">
-        <v>129</v>
-      </c>
-      <c r="CN30" t="s">
-        <v>128</v>
-      </c>
       <c r="CO30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CP30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CQ30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="CR30" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="CS30" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="CT30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Fuel_(petrol-gasoline,_parallel_market)_percentile_classification_matrix.xlsx
+++ b/outputs/Fuel_(petrol-gasoline,_parallel_market)_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2940" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2940" uniqueCount="130">
   <si>
     <t>2018 Mar</t>
   </si>
@@ -403,64 +403,7 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>12%</t>
-  </si>
-  <si>
-    <t>5%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>16%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>19%</t>
-  </si>
-  <si>
-    <t>2%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>9%</t>
-  </si>
-  <si>
-    <t>21%</t>
-  </si>
-  <si>
-    <t>22%</t>
-  </si>
-  <si>
-    <t>17%</t>
-  </si>
-  <si>
-    <t>13%</t>
   </si>
 </sst>
 </file>
@@ -1222,7 +1165,7 @@
         <v>128</v>
       </c>
       <c r="AB2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AC2" t="s">
         <v>128</v>
@@ -1243,7 +1186,7 @@
         <v>127</v>
       </c>
       <c r="AI2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AJ2" t="s">
         <v>128</v>
@@ -1267,16 +1210,16 @@
         <v>128</v>
       </c>
       <c r="AQ2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AR2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AS2" t="s">
         <v>128</v>
       </c>
       <c r="AT2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AU2" t="s">
         <v>127</v>
@@ -1426,13 +1369,13 @@
         <v>127</v>
       </c>
       <c r="CR2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CS2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CT2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:98">
@@ -1608,7 +1551,7 @@
         <v>128</v>
       </c>
       <c r="BF3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BG3" t="s">
         <v>128</v>
@@ -1671,13 +1614,13 @@
         <v>127</v>
       </c>
       <c r="CA3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CB3" t="s">
         <v>127</v>
       </c>
       <c r="CC3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CD3" t="s">
         <v>127</v>
@@ -1701,16 +1644,16 @@
         <v>127</v>
       </c>
       <c r="CK3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CL3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CM3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CN3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CO3" t="s">
         <v>127</v>
@@ -1722,13 +1665,13 @@
         <v>127</v>
       </c>
       <c r="CR3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="CS3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CT3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:98">
@@ -1940,7 +1883,7 @@
         <v>128</v>
       </c>
       <c r="BR4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BS4" t="s">
         <v>128</v>
@@ -1955,76 +1898,76 @@
         <v>127</v>
       </c>
       <c r="BW4" t="s">
+        <v>128</v>
+      </c>
+      <c r="BX4" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY4" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CA4" t="s">
+        <v>128</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>128</v>
+      </c>
+      <c r="CC4" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD4" t="s">
+        <v>128</v>
+      </c>
+      <c r="CE4" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>128</v>
+      </c>
+      <c r="CK4" t="s">
+        <v>128</v>
+      </c>
+      <c r="CL4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM4" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CO4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR4" t="s">
         <v>129</v>
       </c>
-      <c r="BX4" t="s">
-        <v>130</v>
-      </c>
-      <c r="BY4" t="s">
-        <v>130</v>
-      </c>
-      <c r="BZ4" t="s">
-        <v>127</v>
-      </c>
-      <c r="CA4" t="s">
-        <v>130</v>
-      </c>
-      <c r="CB4" t="s">
-        <v>130</v>
-      </c>
-      <c r="CC4" t="s">
-        <v>130</v>
-      </c>
-      <c r="CD4" t="s">
-        <v>130</v>
-      </c>
-      <c r="CE4" t="s">
-        <v>130</v>
-      </c>
-      <c r="CF4" t="s">
-        <v>130</v>
-      </c>
-      <c r="CG4" t="s">
-        <v>130</v>
-      </c>
-      <c r="CH4" t="s">
-        <v>130</v>
-      </c>
-      <c r="CI4" t="s">
-        <v>127</v>
-      </c>
-      <c r="CJ4" t="s">
-        <v>130</v>
-      </c>
-      <c r="CK4" t="s">
-        <v>130</v>
-      </c>
-      <c r="CL4" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM4" t="s">
-        <v>130</v>
-      </c>
-      <c r="CN4" t="s">
-        <v>127</v>
-      </c>
-      <c r="CO4" t="s">
-        <v>127</v>
-      </c>
-      <c r="CP4" t="s">
-        <v>127</v>
-      </c>
-      <c r="CQ4" t="s">
-        <v>127</v>
-      </c>
-      <c r="CR4" t="s">
-        <v>133</v>
-      </c>
       <c r="CS4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="CT4" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:98">
@@ -2248,79 +2191,79 @@
         <v>128</v>
       </c>
       <c r="BV5" t="s">
+        <v>128</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>128</v>
+      </c>
+      <c r="BX5" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ5" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA5" t="s">
+        <v>128</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>128</v>
+      </c>
+      <c r="CC5" t="s">
+        <v>127</v>
+      </c>
+      <c r="CD5" t="s">
+        <v>127</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF5" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH5" t="s">
+        <v>127</v>
+      </c>
+      <c r="CI5" t="s">
+        <v>128</v>
+      </c>
+      <c r="CJ5" t="s">
+        <v>128</v>
+      </c>
+      <c r="CK5" t="s">
+        <v>128</v>
+      </c>
+      <c r="CL5" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM5" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN5" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO5" t="s">
+        <v>127</v>
+      </c>
+      <c r="CP5" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ5" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR5" t="s">
         <v>129</v>
       </c>
-      <c r="BW5" t="s">
-        <v>128</v>
-      </c>
-      <c r="BX5" t="s">
-        <v>128</v>
-      </c>
-      <c r="BY5" t="s">
-        <v>130</v>
-      </c>
-      <c r="BZ5" t="s">
-        <v>130</v>
-      </c>
-      <c r="CA5" t="s">
-        <v>130</v>
-      </c>
-      <c r="CB5" t="s">
-        <v>130</v>
-      </c>
-      <c r="CC5" t="s">
-        <v>127</v>
-      </c>
-      <c r="CD5" t="s">
-        <v>127</v>
-      </c>
-      <c r="CE5" t="s">
-        <v>130</v>
-      </c>
-      <c r="CF5" t="s">
-        <v>130</v>
-      </c>
-      <c r="CG5" t="s">
-        <v>127</v>
-      </c>
-      <c r="CH5" t="s">
-        <v>127</v>
-      </c>
-      <c r="CI5" t="s">
+      <c r="CS5" t="s">
         <v>129</v>
       </c>
-      <c r="CJ5" t="s">
-        <v>130</v>
-      </c>
-      <c r="CK5" t="s">
-        <v>130</v>
-      </c>
-      <c r="CL5" t="s">
-        <v>130</v>
-      </c>
-      <c r="CM5" t="s">
-        <v>130</v>
-      </c>
-      <c r="CN5" t="s">
-        <v>130</v>
-      </c>
-      <c r="CO5" t="s">
-        <v>127</v>
-      </c>
-      <c r="CP5" t="s">
-        <v>127</v>
-      </c>
-      <c r="CQ5" t="s">
-        <v>127</v>
-      </c>
-      <c r="CR5" t="s">
-        <v>134</v>
-      </c>
-      <c r="CS5" t="s">
-        <v>142</v>
-      </c>
       <c r="CT5" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:98">
@@ -2544,79 +2487,79 @@
         <v>128</v>
       </c>
       <c r="BV6" t="s">
+        <v>128</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>128</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>127</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ6" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA6" t="s">
+        <v>127</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>128</v>
+      </c>
+      <c r="CC6" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD6" t="s">
+        <v>128</v>
+      </c>
+      <c r="CE6" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF6" t="s">
+        <v>127</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>127</v>
+      </c>
+      <c r="CI6" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ6" t="s">
+        <v>127</v>
+      </c>
+      <c r="CK6" t="s">
+        <v>127</v>
+      </c>
+      <c r="CL6" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM6" t="s">
+        <v>127</v>
+      </c>
+      <c r="CN6" t="s">
+        <v>127</v>
+      </c>
+      <c r="CO6" t="s">
+        <v>127</v>
+      </c>
+      <c r="CP6" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ6" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR6" t="s">
         <v>129</v>
       </c>
-      <c r="BW6" t="s">
+      <c r="CS6" t="s">
         <v>129</v>
       </c>
-      <c r="BX6" t="s">
-        <v>127</v>
-      </c>
-      <c r="BY6" t="s">
-        <v>130</v>
-      </c>
-      <c r="BZ6" t="s">
-        <v>130</v>
-      </c>
-      <c r="CA6" t="s">
-        <v>127</v>
-      </c>
-      <c r="CB6" t="s">
+      <c r="CT6" t="s">
         <v>129</v>
-      </c>
-      <c r="CC6" t="s">
-        <v>130</v>
-      </c>
-      <c r="CD6" t="s">
-        <v>130</v>
-      </c>
-      <c r="CE6" t="s">
-        <v>130</v>
-      </c>
-      <c r="CF6" t="s">
-        <v>127</v>
-      </c>
-      <c r="CG6" t="s">
-        <v>127</v>
-      </c>
-      <c r="CH6" t="s">
-        <v>127</v>
-      </c>
-      <c r="CI6" t="s">
-        <v>127</v>
-      </c>
-      <c r="CJ6" t="s">
-        <v>127</v>
-      </c>
-      <c r="CK6" t="s">
-        <v>127</v>
-      </c>
-      <c r="CL6" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM6" t="s">
-        <v>127</v>
-      </c>
-      <c r="CN6" t="s">
-        <v>127</v>
-      </c>
-      <c r="CO6" t="s">
-        <v>127</v>
-      </c>
-      <c r="CP6" t="s">
-        <v>127</v>
-      </c>
-      <c r="CQ6" t="s">
-        <v>127</v>
-      </c>
-      <c r="CR6" t="s">
-        <v>135</v>
-      </c>
-      <c r="CS6" t="s">
-        <v>136</v>
-      </c>
-      <c r="CT6" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:98">
@@ -2801,13 +2744,13 @@
         <v>127</v>
       </c>
       <c r="BI7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BJ7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BK7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BL7" t="s">
         <v>127</v>
@@ -2849,7 +2792,7 @@
         <v>127</v>
       </c>
       <c r="BY7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BZ7" t="s">
         <v>128</v>
@@ -2891,7 +2834,7 @@
         <v>128</v>
       </c>
       <c r="CM7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CN7" t="s">
         <v>127</v>
@@ -2906,13 +2849,13 @@
         <v>127</v>
       </c>
       <c r="CR7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CS7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CT7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:98">
@@ -3052,7 +2995,7 @@
         <v>128</v>
       </c>
       <c r="AT8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AU8" t="s">
         <v>128</v>
@@ -3136,79 +3079,79 @@
         <v>128</v>
       </c>
       <c r="BV8" t="s">
+        <v>128</v>
+      </c>
+      <c r="BW8" t="s">
+        <v>127</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ8" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA8" t="s">
+        <v>128</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>128</v>
+      </c>
+      <c r="CC8" t="s">
+        <v>127</v>
+      </c>
+      <c r="CD8" t="s">
+        <v>127</v>
+      </c>
+      <c r="CE8" t="s">
+        <v>127</v>
+      </c>
+      <c r="CF8" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG8" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH8" t="s">
+        <v>127</v>
+      </c>
+      <c r="CI8" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ8" t="s">
+        <v>127</v>
+      </c>
+      <c r="CK8" t="s">
+        <v>127</v>
+      </c>
+      <c r="CL8" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM8" t="s">
+        <v>127</v>
+      </c>
+      <c r="CN8" t="s">
+        <v>127</v>
+      </c>
+      <c r="CO8" t="s">
+        <v>127</v>
+      </c>
+      <c r="CP8" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ8" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR8" t="s">
         <v>129</v>
       </c>
-      <c r="BW8" t="s">
-        <v>127</v>
-      </c>
-      <c r="BX8" t="s">
-        <v>128</v>
-      </c>
-      <c r="BY8" t="s">
-        <v>128</v>
-      </c>
-      <c r="BZ8" t="s">
-        <v>130</v>
-      </c>
-      <c r="CA8" t="s">
-        <v>130</v>
-      </c>
-      <c r="CB8" t="s">
-        <v>130</v>
-      </c>
-      <c r="CC8" t="s">
-        <v>127</v>
-      </c>
-      <c r="CD8" t="s">
-        <v>127</v>
-      </c>
-      <c r="CE8" t="s">
-        <v>127</v>
-      </c>
-      <c r="CF8" t="s">
-        <v>128</v>
-      </c>
-      <c r="CG8" t="s">
-        <v>127</v>
-      </c>
-      <c r="CH8" t="s">
-        <v>127</v>
-      </c>
-      <c r="CI8" t="s">
-        <v>127</v>
-      </c>
-      <c r="CJ8" t="s">
-        <v>127</v>
-      </c>
-      <c r="CK8" t="s">
-        <v>127</v>
-      </c>
-      <c r="CL8" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM8" t="s">
-        <v>127</v>
-      </c>
-      <c r="CN8" t="s">
-        <v>127</v>
-      </c>
-      <c r="CO8" t="s">
-        <v>127</v>
-      </c>
-      <c r="CP8" t="s">
-        <v>127</v>
-      </c>
-      <c r="CQ8" t="s">
-        <v>127</v>
-      </c>
-      <c r="CR8" t="s">
-        <v>136</v>
-      </c>
       <c r="CS8" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="CT8" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:98">
@@ -3498,13 +3441,13 @@
         <v>127</v>
       </c>
       <c r="CR9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CS9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CT9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:98">
@@ -3701,7 +3644,7 @@
         <v>127</v>
       </c>
       <c r="BM10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BN10" t="s">
         <v>127</v>
@@ -3791,16 +3734,16 @@
         <v>127</v>
       </c>
       <c r="CQ10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CR10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CS10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CT10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:98">
@@ -4060,19 +4003,19 @@
         <v>127</v>
       </c>
       <c r="CH11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CI11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CJ11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CK11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CL11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CM11" t="s">
         <v>127</v>
@@ -4090,13 +4033,13 @@
         <v>127</v>
       </c>
       <c r="CR11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CS11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CT11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:98">
@@ -4365,13 +4308,13 @@
         <v>127</v>
       </c>
       <c r="CK12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CL12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CM12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CN12" t="s">
         <v>127</v>
@@ -4386,13 +4329,13 @@
         <v>127</v>
       </c>
       <c r="CR12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CS12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CT12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:98">
@@ -4604,7 +4547,7 @@
         <v>127</v>
       </c>
       <c r="BR13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BS13" t="s">
         <v>127</v>
@@ -4643,7 +4586,7 @@
         <v>127</v>
       </c>
       <c r="CE13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CF13" t="s">
         <v>128</v>
@@ -4655,40 +4598,40 @@
         <v>128</v>
       </c>
       <c r="CI13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CJ13" t="s">
+        <v>128</v>
+      </c>
+      <c r="CK13" t="s">
+        <v>128</v>
+      </c>
+      <c r="CL13" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM13" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN13" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO13" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP13" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ13" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR13" t="s">
         <v>129</v>
       </c>
-      <c r="CK13" t="s">
-        <v>128</v>
-      </c>
-      <c r="CL13" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM13" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN13" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO13" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CQ13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CR13" t="s">
-        <v>137</v>
-      </c>
       <c r="CS13" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="CT13" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:98">
@@ -4885,10 +4828,10 @@
         <v>128</v>
       </c>
       <c r="BM14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BN14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BO14" t="s">
         <v>128</v>
@@ -4903,7 +4846,7 @@
         <v>128</v>
       </c>
       <c r="BS14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BT14" t="s">
         <v>128</v>
@@ -4978,13 +4921,13 @@
         <v>127</v>
       </c>
       <c r="CR14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CS14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CT14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:98">
@@ -5052,7 +4995,7 @@
         <v>127</v>
       </c>
       <c r="V15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="W15" t="s">
         <v>128</v>
@@ -5208,25 +5151,25 @@
         <v>128</v>
       </c>
       <c r="BV15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BW15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BX15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BY15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BZ15" t="s">
         <v>127</v>
       </c>
       <c r="CA15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CB15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CC15" t="s">
         <v>128</v>
@@ -5235,31 +5178,31 @@
         <v>127</v>
       </c>
       <c r="CE15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CF15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CG15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CH15" t="s">
         <v>127</v>
       </c>
       <c r="CI15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CJ15" t="s">
         <v>127</v>
       </c>
       <c r="CK15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CL15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CM15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CN15" t="s">
         <v>127</v>
@@ -5274,13 +5217,13 @@
         <v>127</v>
       </c>
       <c r="CR15" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="CS15" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CT15" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:98">
@@ -5531,52 +5474,52 @@
         <v>128</v>
       </c>
       <c r="CE16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CF16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CG16" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH16" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI16" t="s">
+        <v>128</v>
+      </c>
+      <c r="CJ16" t="s">
+        <v>128</v>
+      </c>
+      <c r="CK16" t="s">
+        <v>128</v>
+      </c>
+      <c r="CL16" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM16" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN16" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO16" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP16" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ16" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR16" t="s">
         <v>129</v>
       </c>
-      <c r="CH16" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI16" t="s">
-        <v>128</v>
-      </c>
-      <c r="CJ16" t="s">
-        <v>128</v>
-      </c>
-      <c r="CK16" t="s">
+      <c r="CS16" t="s">
         <v>129</v>
       </c>
-      <c r="CL16" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM16" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN16" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO16" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP16" t="s">
-        <v>127</v>
-      </c>
-      <c r="CQ16" t="s">
-        <v>127</v>
-      </c>
-      <c r="CR16" t="s">
-        <v>137</v>
-      </c>
-      <c r="CS16" t="s">
-        <v>142</v>
-      </c>
       <c r="CT16" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:98">
@@ -5755,10 +5698,10 @@
         <v>127</v>
       </c>
       <c r="BG17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BH17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BI17" t="s">
         <v>127</v>
@@ -5773,7 +5716,7 @@
         <v>127</v>
       </c>
       <c r="BM17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BN17" t="s">
         <v>128</v>
@@ -5806,7 +5749,7 @@
         <v>128</v>
       </c>
       <c r="BX17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BY17" t="s">
         <v>127</v>
@@ -5821,58 +5764,58 @@
         <v>127</v>
       </c>
       <c r="CC17" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD17" t="s">
+        <v>128</v>
+      </c>
+      <c r="CE17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CF17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CG17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH17" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CK17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CL17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CN17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CO17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CP17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ17" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR17" t="s">
         <v>129</v>
       </c>
-      <c r="CD17" t="s">
-        <v>128</v>
-      </c>
-      <c r="CE17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CF17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CG17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CH17" t="s">
-        <v>128</v>
-      </c>
-      <c r="CI17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CJ17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CK17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CL17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CN17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CO17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CP17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CQ17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CR17" t="s">
-        <v>131</v>
-      </c>
       <c r="CS17" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="CT17" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:98">
@@ -6096,79 +6039,79 @@
         <v>127</v>
       </c>
       <c r="BV18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BW18" t="s">
         <v>128</v>
       </c>
       <c r="BX18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BY18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BZ18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CA18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CB18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CC18" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD18" t="s">
+        <v>128</v>
+      </c>
+      <c r="CE18" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CG18" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH18" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI18" t="s">
+        <v>128</v>
+      </c>
+      <c r="CJ18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CK18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CL18" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM18" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CO18" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR18" t="s">
         <v>129</v>
       </c>
-      <c r="CD18" t="s">
-        <v>130</v>
-      </c>
-      <c r="CE18" t="s">
-        <v>130</v>
-      </c>
-      <c r="CF18" t="s">
-        <v>127</v>
-      </c>
-      <c r="CG18" t="s">
-        <v>130</v>
-      </c>
-      <c r="CH18" t="s">
-        <v>130</v>
-      </c>
-      <c r="CI18" t="s">
-        <v>130</v>
-      </c>
-      <c r="CJ18" t="s">
-        <v>127</v>
-      </c>
-      <c r="CK18" t="s">
-        <v>127</v>
-      </c>
-      <c r="CL18" t="s">
-        <v>130</v>
-      </c>
-      <c r="CM18" t="s">
-        <v>130</v>
-      </c>
-      <c r="CN18" t="s">
-        <v>127</v>
-      </c>
-      <c r="CO18" t="s">
-        <v>130</v>
-      </c>
-      <c r="CP18" t="s">
-        <v>127</v>
-      </c>
-      <c r="CQ18" t="s">
-        <v>127</v>
-      </c>
-      <c r="CR18" t="s">
-        <v>133</v>
-      </c>
       <c r="CS18" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="CT18" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:98">
@@ -6356,115 +6299,115 @@
         <v>128</v>
       </c>
       <c r="BJ19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BO19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BP19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BQ19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BV19" t="s">
+        <v>127</v>
+      </c>
+      <c r="BW19" t="s">
+        <v>127</v>
+      </c>
+      <c r="BX19" t="s">
+        <v>127</v>
+      </c>
+      <c r="BY19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ19" t="s">
+        <v>127</v>
+      </c>
+      <c r="CA19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CC19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CE19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG19" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CJ19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CK19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CL19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CQ19" t="s">
+        <v>128</v>
+      </c>
+      <c r="CR19" t="s">
         <v>129</v>
       </c>
-      <c r="BK19" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL19" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM19" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN19" t="s">
-        <v>128</v>
-      </c>
-      <c r="BO19" t="s">
-        <v>128</v>
-      </c>
-      <c r="BP19" t="s">
-        <v>128</v>
-      </c>
-      <c r="BQ19" t="s">
-        <v>128</v>
-      </c>
-      <c r="BR19" t="s">
+      <c r="CS19" t="s">
         <v>129</v>
       </c>
-      <c r="BS19" t="s">
-        <v>128</v>
-      </c>
-      <c r="BT19" t="s">
+      <c r="CT19" t="s">
         <v>129</v>
-      </c>
-      <c r="BU19" t="s">
-        <v>129</v>
-      </c>
-      <c r="BV19" t="s">
-        <v>127</v>
-      </c>
-      <c r="BW19" t="s">
-        <v>127</v>
-      </c>
-      <c r="BX19" t="s">
-        <v>127</v>
-      </c>
-      <c r="BY19" t="s">
-        <v>129</v>
-      </c>
-      <c r="BZ19" t="s">
-        <v>127</v>
-      </c>
-      <c r="CA19" t="s">
-        <v>129</v>
-      </c>
-      <c r="CB19" t="s">
-        <v>129</v>
-      </c>
-      <c r="CC19" t="s">
-        <v>130</v>
-      </c>
-      <c r="CD19" t="s">
-        <v>130</v>
-      </c>
-      <c r="CE19" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF19" t="s">
-        <v>130</v>
-      </c>
-      <c r="CG19" t="s">
-        <v>127</v>
-      </c>
-      <c r="CH19" t="s">
-        <v>130</v>
-      </c>
-      <c r="CI19" t="s">
-        <v>130</v>
-      </c>
-      <c r="CJ19" t="s">
-        <v>130</v>
-      </c>
-      <c r="CK19" t="s">
-        <v>130</v>
-      </c>
-      <c r="CL19" t="s">
-        <v>130</v>
-      </c>
-      <c r="CM19" t="s">
-        <v>130</v>
-      </c>
-      <c r="CN19" t="s">
-        <v>130</v>
-      </c>
-      <c r="CO19" t="s">
-        <v>130</v>
-      </c>
-      <c r="CP19" t="s">
-        <v>130</v>
-      </c>
-      <c r="CQ19" t="s">
-        <v>130</v>
-      </c>
-      <c r="CR19" t="s">
-        <v>138</v>
-      </c>
-      <c r="CS19" t="s">
-        <v>143</v>
-      </c>
-      <c r="CT19" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:98">
@@ -6583,7 +6526,7 @@
         <v>128</v>
       </c>
       <c r="AM20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AN20" t="s">
         <v>127</v>
@@ -6601,13 +6544,13 @@
         <v>128</v>
       </c>
       <c r="AS20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AT20" t="s">
         <v>128</v>
       </c>
       <c r="AU20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AV20" t="s">
         <v>128</v>
@@ -6631,7 +6574,7 @@
         <v>128</v>
       </c>
       <c r="BC20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BD20" t="s">
         <v>128</v>
@@ -6658,7 +6601,7 @@
         <v>127</v>
       </c>
       <c r="BL20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BM20" t="s">
         <v>128</v>
@@ -6697,7 +6640,7 @@
         <v>127</v>
       </c>
       <c r="BY20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BZ20" t="s">
         <v>127</v>
@@ -6754,13 +6697,13 @@
         <v>127</v>
       </c>
       <c r="CR20" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="CS20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CT20" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:98">
@@ -6981,82 +6924,82 @@
         <v>128</v>
       </c>
       <c r="BU21" t="s">
+        <v>128</v>
+      </c>
+      <c r="BV21" t="s">
+        <v>128</v>
+      </c>
+      <c r="BW21" t="s">
+        <v>127</v>
+      </c>
+      <c r="BX21" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY21" t="s">
+        <v>127</v>
+      </c>
+      <c r="BZ21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CC21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CE21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG21" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CJ21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CK21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CL21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP21" t="s">
+        <v>128</v>
+      </c>
+      <c r="CQ21" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR21" t="s">
         <v>129</v>
       </c>
-      <c r="BV21" t="s">
-        <v>128</v>
-      </c>
-      <c r="BW21" t="s">
-        <v>127</v>
-      </c>
-      <c r="BX21" t="s">
+      <c r="CS21" t="s">
         <v>129</v>
       </c>
-      <c r="BY21" t="s">
-        <v>127</v>
-      </c>
-      <c r="BZ21" t="s">
-        <v>130</v>
-      </c>
-      <c r="CA21" t="s">
-        <v>130</v>
-      </c>
-      <c r="CB21" t="s">
-        <v>130</v>
-      </c>
-      <c r="CC21" t="s">
-        <v>130</v>
-      </c>
-      <c r="CD21" t="s">
-        <v>130</v>
-      </c>
-      <c r="CE21" t="s">
-        <v>130</v>
-      </c>
-      <c r="CF21" t="s">
-        <v>130</v>
-      </c>
-      <c r="CG21" t="s">
-        <v>127</v>
-      </c>
-      <c r="CH21" t="s">
+      <c r="CT21" t="s">
         <v>129</v>
-      </c>
-      <c r="CI21" t="s">
-        <v>130</v>
-      </c>
-      <c r="CJ21" t="s">
-        <v>130</v>
-      </c>
-      <c r="CK21" t="s">
-        <v>130</v>
-      </c>
-      <c r="CL21" t="s">
-        <v>130</v>
-      </c>
-      <c r="CM21" t="s">
-        <v>130</v>
-      </c>
-      <c r="CN21" t="s">
-        <v>130</v>
-      </c>
-      <c r="CO21" t="s">
-        <v>130</v>
-      </c>
-      <c r="CP21" t="s">
-        <v>130</v>
-      </c>
-      <c r="CQ21" t="s">
-        <v>127</v>
-      </c>
-      <c r="CR21" t="s">
-        <v>139</v>
-      </c>
-      <c r="CS21" t="s">
-        <v>136</v>
-      </c>
-      <c r="CT21" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:98">
@@ -7268,7 +7211,7 @@
         <v>127</v>
       </c>
       <c r="BR22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BS22" t="s">
         <v>127</v>
@@ -7280,10 +7223,10 @@
         <v>127</v>
       </c>
       <c r="BV22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BW22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BX22" t="s">
         <v>128</v>
@@ -7307,7 +7250,7 @@
         <v>127</v>
       </c>
       <c r="CE22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CF22" t="s">
         <v>128</v>
@@ -7346,13 +7289,13 @@
         <v>127</v>
       </c>
       <c r="CR22" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CS22" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CT22" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:98">
@@ -7531,7 +7474,7 @@
         <v>128</v>
       </c>
       <c r="BG23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BH23" t="s">
         <v>127</v>
@@ -7573,82 +7516,82 @@
         <v>128</v>
       </c>
       <c r="BU23" t="s">
+        <v>128</v>
+      </c>
+      <c r="BV23" t="s">
+        <v>128</v>
+      </c>
+      <c r="BW23" t="s">
+        <v>128</v>
+      </c>
+      <c r="BX23" t="s">
+        <v>127</v>
+      </c>
+      <c r="BY23" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ23" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA23" t="s">
+        <v>128</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>128</v>
+      </c>
+      <c r="CC23" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CE23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CF23" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CH23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CI23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CJ23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CK23" t="s">
+        <v>128</v>
+      </c>
+      <c r="CL23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM23" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN23" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO23" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ23" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR23" t="s">
         <v>129</v>
       </c>
-      <c r="BV23" t="s">
-        <v>128</v>
-      </c>
-      <c r="BW23" t="s">
-        <v>128</v>
-      </c>
-      <c r="BX23" t="s">
-        <v>128</v>
-      </c>
-      <c r="BY23" t="s">
-        <v>130</v>
-      </c>
-      <c r="BZ23" t="s">
-        <v>130</v>
-      </c>
-      <c r="CA23" t="s">
-        <v>128</v>
-      </c>
-      <c r="CB23" t="s">
-        <v>128</v>
-      </c>
-      <c r="CC23" t="s">
-        <v>128</v>
-      </c>
-      <c r="CD23" t="s">
-        <v>127</v>
-      </c>
-      <c r="CE23" t="s">
-        <v>127</v>
-      </c>
-      <c r="CF23" t="s">
-        <v>130</v>
-      </c>
-      <c r="CG23" t="s">
-        <v>127</v>
-      </c>
-      <c r="CH23" t="s">
-        <v>127</v>
-      </c>
-      <c r="CI23" t="s">
-        <v>127</v>
-      </c>
-      <c r="CJ23" t="s">
-        <v>127</v>
-      </c>
-      <c r="CK23" t="s">
-        <v>130</v>
-      </c>
-      <c r="CL23" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM23" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN23" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO23" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP23" t="s">
-        <v>127</v>
-      </c>
-      <c r="CQ23" t="s">
-        <v>127</v>
-      </c>
-      <c r="CR23" t="s">
-        <v>140</v>
-      </c>
       <c r="CS23" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="CT23" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:98">
@@ -7872,79 +7815,79 @@
         <v>128</v>
       </c>
       <c r="BV24" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BW24" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BX24" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY24" t="s">
+        <v>127</v>
+      </c>
+      <c r="BZ24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CC24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CE24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CJ24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CK24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CL24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CQ24" t="s">
+        <v>128</v>
+      </c>
+      <c r="CR24" t="s">
         <v>129</v>
       </c>
-      <c r="BY24" t="s">
-        <v>127</v>
-      </c>
-      <c r="BZ24" t="s">
-        <v>130</v>
-      </c>
-      <c r="CA24" t="s">
-        <v>130</v>
-      </c>
-      <c r="CB24" t="s">
+      <c r="CS24" t="s">
         <v>129</v>
       </c>
-      <c r="CC24" t="s">
+      <c r="CT24" t="s">
         <v>129</v>
-      </c>
-      <c r="CD24" t="s">
-        <v>130</v>
-      </c>
-      <c r="CE24" t="s">
-        <v>130</v>
-      </c>
-      <c r="CF24" t="s">
-        <v>130</v>
-      </c>
-      <c r="CG24" t="s">
-        <v>130</v>
-      </c>
-      <c r="CH24" t="s">
-        <v>130</v>
-      </c>
-      <c r="CI24" t="s">
-        <v>130</v>
-      </c>
-      <c r="CJ24" t="s">
-        <v>130</v>
-      </c>
-      <c r="CK24" t="s">
-        <v>130</v>
-      </c>
-      <c r="CL24" t="s">
-        <v>130</v>
-      </c>
-      <c r="CM24" t="s">
-        <v>130</v>
-      </c>
-      <c r="CN24" t="s">
-        <v>130</v>
-      </c>
-      <c r="CO24" t="s">
-        <v>130</v>
-      </c>
-      <c r="CP24" t="s">
-        <v>130</v>
-      </c>
-      <c r="CQ24" t="s">
-        <v>130</v>
-      </c>
-      <c r="CR24" t="s">
-        <v>141</v>
-      </c>
-      <c r="CS24" t="s">
-        <v>136</v>
-      </c>
-      <c r="CT24" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:98">
@@ -8168,79 +8111,79 @@
         <v>127</v>
       </c>
       <c r="BV25" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BW25" t="s">
+        <v>128</v>
+      </c>
+      <c r="BX25" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY25" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CC25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CE25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CJ25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CK25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CL25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM25" t="s">
+        <v>127</v>
+      </c>
+      <c r="CN25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CQ25" t="s">
+        <v>128</v>
+      </c>
+      <c r="CR25" t="s">
         <v>129</v>
       </c>
-      <c r="BX25" t="s">
-        <v>128</v>
-      </c>
-      <c r="BY25" t="s">
-        <v>130</v>
-      </c>
-      <c r="BZ25" t="s">
-        <v>130</v>
-      </c>
-      <c r="CA25" t="s">
-        <v>130</v>
-      </c>
-      <c r="CB25" t="s">
-        <v>130</v>
-      </c>
-      <c r="CC25" t="s">
-        <v>130</v>
-      </c>
-      <c r="CD25" t="s">
-        <v>128</v>
-      </c>
-      <c r="CE25" t="s">
-        <v>130</v>
-      </c>
-      <c r="CF25" t="s">
-        <v>130</v>
-      </c>
-      <c r="CG25" t="s">
-        <v>128</v>
-      </c>
-      <c r="CH25" t="s">
-        <v>130</v>
-      </c>
-      <c r="CI25" t="s">
-        <v>130</v>
-      </c>
-      <c r="CJ25" t="s">
-        <v>128</v>
-      </c>
-      <c r="CK25" t="s">
-        <v>130</v>
-      </c>
-      <c r="CL25" t="s">
-        <v>130</v>
-      </c>
-      <c r="CM25" t="s">
-        <v>127</v>
-      </c>
-      <c r="CN25" t="s">
-        <v>130</v>
-      </c>
-      <c r="CO25" t="s">
-        <v>130</v>
-      </c>
-      <c r="CP25" t="s">
-        <v>128</v>
-      </c>
-      <c r="CQ25" t="s">
-        <v>130</v>
-      </c>
-      <c r="CR25" t="s">
-        <v>139</v>
-      </c>
       <c r="CS25" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="CT25" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:98">
@@ -8479,22 +8422,22 @@
         <v>128</v>
       </c>
       <c r="CA26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CB26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CC26" t="s">
         <v>127</v>
       </c>
       <c r="CD26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CE26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CF26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CG26" t="s">
         <v>128</v>
@@ -8530,13 +8473,13 @@
         <v>127</v>
       </c>
       <c r="CR26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CS26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CT26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:98">
@@ -8550,7 +8493,7 @@
         <v>128</v>
       </c>
       <c r="D27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E27" t="s">
         <v>127</v>
@@ -8715,10 +8658,10 @@
         <v>127</v>
       </c>
       <c r="BG27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BH27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BI27" t="s">
         <v>128</v>
@@ -8730,25 +8673,25 @@
         <v>127</v>
       </c>
       <c r="BL27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BM27" t="s">
         <v>127</v>
       </c>
       <c r="BN27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BO27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BP27" t="s">
         <v>127</v>
       </c>
       <c r="BQ27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BR27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BS27" t="s">
         <v>127</v>
@@ -8826,13 +8769,13 @@
         <v>127</v>
       </c>
       <c r="CR27" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CS27" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="CT27" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:98">
@@ -9080,13 +9023,13 @@
         <v>128</v>
       </c>
       <c r="CD28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="CE28" t="s">
         <v>128</v>
       </c>
       <c r="CF28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="CG28" t="s">
         <v>128</v>
@@ -9098,37 +9041,37 @@
         <v>128</v>
       </c>
       <c r="CJ28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CK28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CL28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO28" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP28" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ28" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR28" t="s">
         <v>129</v>
       </c>
-      <c r="CK28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CL28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CN28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CO28" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP28" t="s">
-        <v>127</v>
-      </c>
-      <c r="CQ28" t="s">
-        <v>127</v>
-      </c>
-      <c r="CR28" t="s">
-        <v>137</v>
-      </c>
       <c r="CS28" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="CT28" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:98">
@@ -9334,97 +9277,97 @@
         <v>128</v>
       </c>
       <c r="BP29" t="s">
+        <v>128</v>
+      </c>
+      <c r="BQ29" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR29" t="s">
+        <v>128</v>
+      </c>
+      <c r="BS29" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT29" t="s">
+        <v>127</v>
+      </c>
+      <c r="BU29" t="s">
+        <v>128</v>
+      </c>
+      <c r="BV29" t="s">
+        <v>128</v>
+      </c>
+      <c r="BW29" t="s">
+        <v>128</v>
+      </c>
+      <c r="BX29" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY29" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CC29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CE29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CJ29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CK29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CL29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CM29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CO29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CP29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CQ29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CR29" t="s">
         <v>129</v>
       </c>
-      <c r="BQ29" t="s">
-        <v>128</v>
-      </c>
-      <c r="BR29" t="s">
-        <v>128</v>
-      </c>
-      <c r="BS29" t="s">
-        <v>128</v>
-      </c>
-      <c r="BT29" t="s">
-        <v>127</v>
-      </c>
-      <c r="BU29" t="s">
+      <c r="CS29" t="s">
         <v>129</v>
       </c>
-      <c r="BV29" t="s">
+      <c r="CT29" t="s">
         <v>129</v>
-      </c>
-      <c r="BW29" t="s">
-        <v>130</v>
-      </c>
-      <c r="BX29" t="s">
-        <v>129</v>
-      </c>
-      <c r="BY29" t="s">
-        <v>129</v>
-      </c>
-      <c r="BZ29" t="s">
-        <v>129</v>
-      </c>
-      <c r="CA29" t="s">
-        <v>129</v>
-      </c>
-      <c r="CB29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CC29" t="s">
-        <v>130</v>
-      </c>
-      <c r="CD29" t="s">
-        <v>130</v>
-      </c>
-      <c r="CE29" t="s">
-        <v>130</v>
-      </c>
-      <c r="CF29" t="s">
-        <v>130</v>
-      </c>
-      <c r="CG29" t="s">
-        <v>130</v>
-      </c>
-      <c r="CH29" t="s">
-        <v>130</v>
-      </c>
-      <c r="CI29" t="s">
-        <v>130</v>
-      </c>
-      <c r="CJ29" t="s">
-        <v>130</v>
-      </c>
-      <c r="CK29" t="s">
-        <v>130</v>
-      </c>
-      <c r="CL29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM29" t="s">
-        <v>130</v>
-      </c>
-      <c r="CN29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CO29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CP29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CQ29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CR29" t="s">
-        <v>134</v>
-      </c>
-      <c r="CS29" t="s">
-        <v>143</v>
-      </c>
-      <c r="CT29" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:98">
@@ -9648,79 +9591,79 @@
         <v>128</v>
       </c>
       <c r="BV30" t="s">
+        <v>128</v>
+      </c>
+      <c r="BW30" t="s">
+        <v>128</v>
+      </c>
+      <c r="BX30" t="s">
+        <v>128</v>
+      </c>
+      <c r="BY30" t="s">
+        <v>128</v>
+      </c>
+      <c r="BZ30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CA30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CC30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CE30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CF30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CG30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CH30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CI30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CJ30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CK30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CL30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CM30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CN30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CQ30" t="s">
+        <v>128</v>
+      </c>
+      <c r="CR30" t="s">
         <v>129</v>
       </c>
-      <c r="BW30" t="s">
+      <c r="CS30" t="s">
         <v>129</v>
       </c>
-      <c r="BX30" t="s">
-        <v>128</v>
-      </c>
-      <c r="BY30" t="s">
+      <c r="CT30" t="s">
         <v>129</v>
-      </c>
-      <c r="BZ30" t="s">
-        <v>128</v>
-      </c>
-      <c r="CA30" t="s">
-        <v>130</v>
-      </c>
-      <c r="CB30" t="s">
-        <v>129</v>
-      </c>
-      <c r="CC30" t="s">
-        <v>128</v>
-      </c>
-      <c r="CD30" t="s">
-        <v>128</v>
-      </c>
-      <c r="CE30" t="s">
-        <v>128</v>
-      </c>
-      <c r="CF30" t="s">
-        <v>130</v>
-      </c>
-      <c r="CG30" t="s">
-        <v>130</v>
-      </c>
-      <c r="CH30" t="s">
-        <v>130</v>
-      </c>
-      <c r="CI30" t="s">
-        <v>130</v>
-      </c>
-      <c r="CJ30" t="s">
-        <v>128</v>
-      </c>
-      <c r="CK30" t="s">
-        <v>129</v>
-      </c>
-      <c r="CL30" t="s">
-        <v>128</v>
-      </c>
-      <c r="CM30" t="s">
-        <v>130</v>
-      </c>
-      <c r="CN30" t="s">
-        <v>129</v>
-      </c>
-      <c r="CO30" t="s">
-        <v>128</v>
-      </c>
-      <c r="CP30" t="s">
-        <v>128</v>
-      </c>
-      <c r="CQ30" t="s">
-        <v>128</v>
-      </c>
-      <c r="CR30" t="s">
-        <v>132</v>
-      </c>
-      <c r="CS30" t="s">
-        <v>132</v>
-      </c>
-      <c r="CT30" t="s">
-        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Fuel_(petrol-gasoline,_parallel_market)_percentile_classification_matrix.xlsx
+++ b/outputs/Fuel_(petrol-gasoline,_parallel_market)_percentile_classification_matrix.xlsx
@@ -400,7 +400,7 @@
     <t>No data</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>0%</t>
